--- a/PAMF_DIG F2 - monthly2026-07-26.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-26.xlsx
@@ -925,7 +925,7 @@
         <v>0.09</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>0.09</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-26.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-26.xlsx
@@ -560,7 +560,7 @@
         <v>0.09</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>0.09</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>0.09</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>0.09</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>0.09</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>0.09</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>0.09</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>0.09</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>0.09</v>
       </c>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>0.09</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>0.09</v>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0.09</v>
       </c>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>0.09</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>0.09</v>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>0.09</v>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>0.09</v>
       </c>
       <c r="N152" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>0.09</v>
       </c>
       <c r="N174" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>0.09</v>
       </c>
       <c r="N175" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
